--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W351"/>
+  <dimension ref="A1:W355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26739,6 +26739,306 @@
         <v>329.56</v>
       </c>
       <c r="W351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>279.89</v>
+      </c>
+      <c r="C352" t="n">
+        <v>274.11</v>
+      </c>
+      <c r="D352" t="n">
+        <v>283.51</v>
+      </c>
+      <c r="E352" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="F352" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="G352" t="n">
+        <v>293.49</v>
+      </c>
+      <c r="H352" t="n">
+        <v>292.45</v>
+      </c>
+      <c r="I352" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="J352" t="n">
+        <v>306.93</v>
+      </c>
+      <c r="K352" t="n">
+        <v>316.63</v>
+      </c>
+      <c r="L352" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="M352" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="N352" t="n">
+        <v>326.56</v>
+      </c>
+      <c r="O352" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="P352" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="R352" t="n">
+        <v>325.17</v>
+      </c>
+      <c r="S352" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="T352" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="U352" t="n">
+        <v>321.22</v>
+      </c>
+      <c r="V352" t="n">
+        <v>326.89</v>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="C353" t="n">
+        <v>272.01</v>
+      </c>
+      <c r="D353" t="n">
+        <v>282.51</v>
+      </c>
+      <c r="E353" t="n">
+        <v>293.18</v>
+      </c>
+      <c r="F353" t="n">
+        <v>299.27</v>
+      </c>
+      <c r="G353" t="n">
+        <v>293.87</v>
+      </c>
+      <c r="H353" t="n">
+        <v>292.45</v>
+      </c>
+      <c r="I353" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="J353" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="K353" t="n">
+        <v>315.49</v>
+      </c>
+      <c r="L353" t="n">
+        <v>317.62</v>
+      </c>
+      <c r="M353" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="N353" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="O353" t="n">
+        <v>325.57</v>
+      </c>
+      <c r="P353" t="n">
+        <v>325.76</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>325.46</v>
+      </c>
+      <c r="R353" t="n">
+        <v>322.17</v>
+      </c>
+      <c r="S353" t="n">
+        <v>321.29</v>
+      </c>
+      <c r="T353" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="U353" t="n">
+        <v>316.91</v>
+      </c>
+      <c r="V353" t="n">
+        <v>322.68</v>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>279.02</v>
+      </c>
+      <c r="C354" t="n">
+        <v>273.98</v>
+      </c>
+      <c r="D354" t="n">
+        <v>283.69</v>
+      </c>
+      <c r="E354" t="n">
+        <v>294.29</v>
+      </c>
+      <c r="F354" t="n">
+        <v>299.66</v>
+      </c>
+      <c r="G354" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="H354" t="n">
+        <v>293.44</v>
+      </c>
+      <c r="I354" t="n">
+        <v>300.79</v>
+      </c>
+      <c r="J354" t="n">
+        <v>307.02</v>
+      </c>
+      <c r="K354" t="n">
+        <v>316.71</v>
+      </c>
+      <c r="L354" t="n">
+        <v>319</v>
+      </c>
+      <c r="M354" t="n">
+        <v>323.46</v>
+      </c>
+      <c r="N354" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="O354" t="n">
+        <v>325.91</v>
+      </c>
+      <c r="P354" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>325.84</v>
+      </c>
+      <c r="R354" t="n">
+        <v>323.03</v>
+      </c>
+      <c r="S354" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="T354" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="U354" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="V354" t="n">
+        <v>322.82</v>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>280.28</v>
+      </c>
+      <c r="C355" t="n">
+        <v>274.88</v>
+      </c>
+      <c r="D355" t="n">
+        <v>283.32</v>
+      </c>
+      <c r="E355" t="n">
+        <v>294.53</v>
+      </c>
+      <c r="F355" t="n">
+        <v>299</v>
+      </c>
+      <c r="G355" t="n">
+        <v>294.26</v>
+      </c>
+      <c r="H355" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="I355" t="n">
+        <v>300.67</v>
+      </c>
+      <c r="J355" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="K355" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="L355" t="n">
+        <v>318.64</v>
+      </c>
+      <c r="M355" t="n">
+        <v>322.93</v>
+      </c>
+      <c r="N355" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="O355" t="n">
+        <v>325.86</v>
+      </c>
+      <c r="P355" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>325.96</v>
+      </c>
+      <c r="R355" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="S355" t="n">
+        <v>320.9</v>
+      </c>
+      <c r="T355" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="U355" t="n">
+        <v>316.17</v>
+      </c>
+      <c r="V355" t="n">
+        <v>322.15</v>
+      </c>
+      <c r="W355" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26755,7 +27055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30298,6 +30598,46 @@
       </c>
       <c r="B354" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -30466,28 +30806,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3905250189848118</v>
+        <v>0.360785271818921</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02740149526384994</v>
+        <v>0.02388446653043341</v>
       </c>
       <c r="M2" t="n">
-        <v>14.62968173740889</v>
+        <v>14.6359873477412</v>
       </c>
       <c r="N2" t="n">
-        <v>305.3997084800716</v>
+        <v>304.0043809182779</v>
       </c>
       <c r="O2" t="n">
-        <v>17.47568907025046</v>
+        <v>17.4357214051578</v>
       </c>
       <c r="P2" t="n">
-        <v>282.1778696335095</v>
+        <v>282.5002562464606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30544,28 +30884,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3048412533181628</v>
+        <v>0.2658593374681786</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03617328438363565</v>
+        <v>0.0277298111146268</v>
       </c>
       <c r="M3" t="n">
-        <v>9.264076806667061</v>
+        <v>9.365904888234185</v>
       </c>
       <c r="N3" t="n">
-        <v>138.495919166939</v>
+        <v>140.4249760746235</v>
       </c>
       <c r="O3" t="n">
-        <v>11.76842891667953</v>
+        <v>11.85010447526196</v>
       </c>
       <c r="P3" t="n">
-        <v>283.3583463790254</v>
+        <v>283.7832117158325</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30622,28 +30962,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2844535552492758</v>
+        <v>0.2649323615520233</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06560752154902916</v>
+        <v>0.0579879079080402</v>
       </c>
       <c r="M4" t="n">
-        <v>6.673446951330925</v>
+        <v>6.692804661206342</v>
       </c>
       <c r="N4" t="n">
-        <v>64.87556404927568</v>
+        <v>65.02556677133872</v>
       </c>
       <c r="O4" t="n">
-        <v>8.054536861252526</v>
+        <v>8.063843176261473</v>
       </c>
       <c r="P4" t="n">
-        <v>284.5635075042729</v>
+        <v>284.7752253176993</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30700,28 +31040,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.244485028205283</v>
+        <v>0.2240323337586957</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06671132696992532</v>
+        <v>0.05681567210128435</v>
       </c>
       <c r="M5" t="n">
-        <v>5.705918517628586</v>
+        <v>5.745305072173358</v>
       </c>
       <c r="N5" t="n">
-        <v>47.07644568148238</v>
+        <v>47.51655222836266</v>
       </c>
       <c r="O5" t="n">
-        <v>6.861227709490655</v>
+        <v>6.893225096307436</v>
       </c>
       <c r="P5" t="n">
-        <v>296.6153018197363</v>
+        <v>296.8371095559792</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30778,28 +31118,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1739298967847511</v>
+        <v>0.1498769031512799</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04718588678595925</v>
+        <v>0.03497975741214165</v>
       </c>
       <c r="M6" t="n">
-        <v>4.804388504172066</v>
+        <v>4.885518669388741</v>
       </c>
       <c r="N6" t="n">
-        <v>34.38961000825126</v>
+        <v>35.34143173818772</v>
       </c>
       <c r="O6" t="n">
-        <v>5.864265513109998</v>
+        <v>5.944865998337366</v>
       </c>
       <c r="P6" t="n">
-        <v>305.5575633683845</v>
+        <v>305.8184301816314</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30856,28 +31196,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1211114794374753</v>
+        <v>0.1035666529261845</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02431308060703052</v>
+        <v>0.01793999657019851</v>
       </c>
       <c r="M7" t="n">
-        <v>4.64296502716592</v>
+        <v>4.683601386858141</v>
       </c>
       <c r="N7" t="n">
-        <v>33.46902319782212</v>
+        <v>33.8171085000653</v>
       </c>
       <c r="O7" t="n">
-        <v>5.785241844367625</v>
+        <v>5.815247931091615</v>
       </c>
       <c r="P7" t="n">
-        <v>298.9809246021682</v>
+        <v>299.1698783189907</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30934,28 +31274,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1226377910344664</v>
+        <v>0.1075314194379489</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03039567375310126</v>
+        <v>0.02364086382961861</v>
       </c>
       <c r="M8" t="n">
-        <v>4.159699579146442</v>
+        <v>4.191129208880726</v>
       </c>
       <c r="N8" t="n">
-        <v>27.00934928396149</v>
+        <v>27.2340416908786</v>
       </c>
       <c r="O8" t="n">
-        <v>5.197051980109636</v>
+        <v>5.218624501808748</v>
       </c>
       <c r="P8" t="n">
-        <v>296.4923018760339</v>
+        <v>296.6561319125174</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31012,28 +31352,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1592071926483322</v>
+        <v>0.1491550853452113</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04084392408629844</v>
+        <v>0.03661819200371319</v>
       </c>
       <c r="M9" t="n">
-        <v>4.749054828768503</v>
+        <v>4.748831194135039</v>
       </c>
       <c r="N9" t="n">
-        <v>33.50965086341295</v>
+        <v>33.37895692912486</v>
       </c>
       <c r="O9" t="n">
-        <v>5.788752098977201</v>
+        <v>5.777452460135424</v>
       </c>
       <c r="P9" t="n">
-        <v>299.998576405364</v>
+        <v>300.107570653991</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31090,28 +31430,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09719181980458927</v>
+        <v>0.08085645300390649</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01821630020658016</v>
+        <v>0.01271177854146122</v>
       </c>
       <c r="M10" t="n">
-        <v>4.387156477267755</v>
+        <v>4.413277067202875</v>
       </c>
       <c r="N10" t="n">
-        <v>28.66142523235528</v>
+        <v>28.95756881524193</v>
       </c>
       <c r="O10" t="n">
-        <v>5.353636636189953</v>
+        <v>5.381223728413634</v>
       </c>
       <c r="P10" t="n">
-        <v>311.6309694279792</v>
+        <v>311.8081319897843</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31168,28 +31508,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05961668352767369</v>
+        <v>0.04806982065593815</v>
       </c>
       <c r="J11" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007899963943805655</v>
+        <v>0.005212295861693916</v>
       </c>
       <c r="M11" t="n">
-        <v>4.108881588883514</v>
+        <v>4.127628163643214</v>
       </c>
       <c r="N11" t="n">
-        <v>24.88004050744859</v>
+        <v>24.90445226817645</v>
       </c>
       <c r="O11" t="n">
-        <v>4.987989625836104</v>
+        <v>4.990436079960994</v>
       </c>
       <c r="P11" t="n">
-        <v>319.9301708034204</v>
+        <v>320.0562659540278</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31246,28 +31586,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1436155266602134</v>
+        <v>0.130291502965083</v>
       </c>
       <c r="J12" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05752688952752483</v>
+        <v>0.0479531337107425</v>
       </c>
       <c r="M12" t="n">
-        <v>3.451977553084017</v>
+        <v>3.487513134194399</v>
       </c>
       <c r="N12" t="n">
-        <v>18.8358822945726</v>
+        <v>19.03286485611118</v>
       </c>
       <c r="O12" t="n">
-        <v>4.340032522294344</v>
+        <v>4.362667172282476</v>
       </c>
       <c r="P12" t="n">
-        <v>320.9077439416218</v>
+        <v>321.0532504023805</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31324,28 +31664,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08188895943184447</v>
+        <v>0.07280834420758309</v>
       </c>
       <c r="J13" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01500176406867593</v>
+        <v>0.01208991092325939</v>
       </c>
       <c r="M13" t="n">
-        <v>3.713154934812454</v>
+        <v>3.717878151663915</v>
       </c>
       <c r="N13" t="n">
-        <v>25.03489377472853</v>
+        <v>24.94810422184958</v>
       </c>
       <c r="O13" t="n">
-        <v>5.003488160746314</v>
+        <v>4.994807726214251</v>
       </c>
       <c r="P13" t="n">
-        <v>325.0531227062443</v>
+        <v>325.1509248286324</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31402,28 +31742,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1168862580321824</v>
+        <v>0.1058986128925638</v>
       </c>
       <c r="J14" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02677867200524842</v>
+        <v>0.02239080933444615</v>
       </c>
       <c r="M14" t="n">
-        <v>4.228128750988977</v>
+        <v>4.238895596760202</v>
       </c>
       <c r="N14" t="n">
-        <v>28.23263536904696</v>
+        <v>28.20050906261795</v>
       </c>
       <c r="O14" t="n">
-        <v>5.313439128196253</v>
+        <v>5.310415149742809</v>
       </c>
       <c r="P14" t="n">
-        <v>328.5623415467305</v>
+        <v>328.6806738625826</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31480,28 +31820,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1098979764363839</v>
+        <v>0.09955581288233654</v>
       </c>
       <c r="J15" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01989888083096913</v>
+        <v>0.01665683245661587</v>
       </c>
       <c r="M15" t="n">
-        <v>4.802123405914534</v>
+        <v>4.798041193256213</v>
       </c>
       <c r="N15" t="n">
-        <v>33.82388988774137</v>
+        <v>33.69976354644027</v>
       </c>
       <c r="O15" t="n">
-        <v>5.815830971386752</v>
+        <v>5.805149743670723</v>
       </c>
       <c r="P15" t="n">
-        <v>328.0559139276143</v>
+        <v>328.1673153073896</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31558,28 +31898,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05914357849430447</v>
+        <v>0.05050403075400599</v>
       </c>
       <c r="J16" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K16" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006115855715089547</v>
+        <v>0.004550690819305592</v>
       </c>
       <c r="M16" t="n">
-        <v>4.616424050998802</v>
+        <v>4.610732681778701</v>
       </c>
       <c r="N16" t="n">
-        <v>31.68683256153155</v>
+        <v>31.50826887175585</v>
       </c>
       <c r="O16" t="n">
-        <v>5.629105840320605</v>
+        <v>5.613222681468806</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0564952989362</v>
+        <v>329.1508574790944</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31636,28 +31976,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09654274981432456</v>
+        <v>0.08151023523899074</v>
       </c>
       <c r="J17" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K17" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01085139327250895</v>
+        <v>0.007859834374325247</v>
       </c>
       <c r="M17" t="n">
-        <v>5.698838682420467</v>
+        <v>5.70213569447555</v>
       </c>
       <c r="N17" t="n">
-        <v>47.35877618827311</v>
+        <v>47.3603138816183</v>
       </c>
       <c r="O17" t="n">
-        <v>6.881771297294986</v>
+        <v>6.881883018594424</v>
       </c>
       <c r="P17" t="n">
-        <v>330.8344606783705</v>
+        <v>330.9986460724975</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31714,28 +32054,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1039900761586774</v>
+        <v>0.08781326524929094</v>
       </c>
       <c r="J18" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K18" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01430353441515941</v>
+        <v>0.01033984003955513</v>
       </c>
       <c r="M18" t="n">
-        <v>5.296443063059072</v>
+        <v>5.31222141456718</v>
       </c>
       <c r="N18" t="n">
-        <v>41.54021387443019</v>
+        <v>41.6795634490805</v>
       </c>
       <c r="O18" t="n">
-        <v>6.445169809588433</v>
+        <v>6.455971146859356</v>
       </c>
       <c r="P18" t="n">
-        <v>327.9277651620789</v>
+        <v>328.1044367956002</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31792,28 +32132,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.149275888028101</v>
+        <v>0.1326809917920969</v>
       </c>
       <c r="J19" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K19" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02040791242841744</v>
+        <v>0.016399700906082</v>
       </c>
       <c r="M19" t="n">
-        <v>6.445678747496547</v>
+        <v>6.460558469507879</v>
       </c>
       <c r="N19" t="n">
-        <v>60.21555946049084</v>
+        <v>60.21368838815928</v>
       </c>
       <c r="O19" t="n">
-        <v>7.759868520825004</v>
+        <v>7.75974795906151</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8771604281824</v>
+        <v>326.057182746849</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31870,28 +32210,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08877356458046648</v>
+        <v>0.06895157043350846</v>
       </c>
       <c r="J20" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K20" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007695836907684828</v>
+        <v>0.004693521684171365</v>
       </c>
       <c r="M20" t="n">
-        <v>6.431320803972854</v>
+        <v>6.45438940883668</v>
       </c>
       <c r="N20" t="n">
-        <v>57.2056583087274</v>
+        <v>57.49650072478298</v>
       </c>
       <c r="O20" t="n">
-        <v>7.563442226177668</v>
+        <v>7.582644705166066</v>
       </c>
       <c r="P20" t="n">
-        <v>327.8767492187337</v>
+        <v>328.0917606417262</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31948,28 +32288,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1690483728306819</v>
+        <v>0.1453150013985004</v>
       </c>
       <c r="J21" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K21" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01878146938139713</v>
+        <v>0.01405957377975697</v>
       </c>
       <c r="M21" t="n">
-        <v>7.624283546615199</v>
+        <v>7.650692864384577</v>
       </c>
       <c r="N21" t="n">
-        <v>84.05061137365961</v>
+        <v>84.44899930263101</v>
       </c>
       <c r="O21" t="n">
-        <v>9.167912050933932</v>
+        <v>9.189613664492704</v>
       </c>
       <c r="P21" t="n">
-        <v>324.0937411190541</v>
+        <v>324.3511879931287</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32026,28 +32366,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.127501215161482</v>
+        <v>0.1095552097710625</v>
       </c>
       <c r="J22" t="n">
+        <v>354</v>
+      </c>
+      <c r="K22" t="n">
         <v>350</v>
       </c>
-      <c r="K22" t="n">
-        <v>346</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01397714516917703</v>
+        <v>0.01048071338664502</v>
       </c>
       <c r="M22" t="n">
-        <v>6.577977353289064</v>
+        <v>6.586555588830413</v>
       </c>
       <c r="N22" t="n">
-        <v>64.9384202703577</v>
+        <v>64.9893923838372</v>
       </c>
       <c r="O22" t="n">
-        <v>8.058437830644205</v>
+        <v>8.0615998650291</v>
       </c>
       <c r="P22" t="n">
-        <v>328.449403887234</v>
+        <v>328.6438520360383</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32085,7 +32425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W351"/>
+  <dimension ref="A1:W355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73047,6 +73387,474 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-36.706958881415915,175.60879521230177</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-36.7075786781049,175.6092596470865</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-36.708117917892025,175.60986133592942</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-36.70865561372249,175.61046564757018</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-36.70922895828638,175.61104587251222</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-36.70984421486462,175.6115850617867</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-36.71040220297681,175.61217858985717</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-36.71091054467033,175.6128162553201</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-36.71140858531035,175.61349324073936</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-36.711880536159576,175.61422362719964</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-36.712340889620215,175.61494096353724</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-36.712785483855086,175.61565246195235</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-36.71323159115644,175.61637748232735</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-36.713652432990294,175.6171216951402</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-36.714068296354355,175.61785491344492</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-36.71449226135683,175.61860010184913</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-36.714897913255086,175.61936447949614</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>-36.71525927514942,175.62014270957746</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>-36.71564227471382,175.62091906991682</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>-36.71599393880162,175.62171969270008</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>-36.71627023574047,175.62255141346515</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-36.706974641570355,175.60876835840074</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-36.70758982169573,175.60924065937832</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-36.70812322439619,175.6098522941347</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-36.70865571985323,175.61046546673373</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-36.70922635796358,175.61105002279766</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-36.70984197223206,175.61158827424447</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-36.71040220297681,175.61217858985717</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-36.71090334881499,175.61282612525125</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-36.71141500631458,175.61348492075066</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-36.7118881496117,175.61421506616333</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-36.712354329869086,175.61492708761227</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-36.7127930897202,175.6156447476379</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-36.71323721641447,175.61637225186638</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-36.7136669880495,175.61710908224464</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-36.71408765390609,175.61783813897455</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-36.71451981741781,175.61857843838953</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-36.71492141415742,175.61934790176628</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-36.71529332897966,175.62011884963943</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-36.715674121420165,175.62089836612262</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>-36.71602892505985,175.62169877644283</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>-36.71630444616747,175.62253107542674</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-36.7069634980274,175.60878734600868</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-36.707579367946316,175.6092584716571</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-36.7081169627212,175.60986296345237</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-36.708649829597164,175.61047550315692</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-36.709224200248805,175.61105346665133</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-36.70983648368363,175.61159613631133</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-36.710396216538086,175.6121868009605</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-36.710893734183564,175.61283931280343</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-36.7114080242517,175.6134939677286</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-36.71188000188222,175.61422422797403</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-36.71234476927984,175.61493695811612</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-36.71278541407651,175.61565253272585</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-36.71322791310299,175.61638090224372</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-36.7136644760089,175.61711125908988</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-36.71408329476294,175.61784191643233</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-36.7145169247928,175.61858071245507</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-36.7149146772323,175.61935265404986</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>-36.71529356437479,175.62011868470893</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>-36.71566885354414,175.6209017908115</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>-36.7160311167743,175.62169746614305</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>-36.716303308528616,175.62253175175132</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-36.706956811900255,175.60879873857078</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-36.707574592120885,175.60926660924477</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-36.70811892612787,175.60985961798855</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-36.70864855602819,175.61047767319417</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-36.70922785176605,175.61104763859117</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-36.709839670582774,175.61159157124038</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-36.71039857483219,175.6121835662836</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-36.710894459816174,175.61283831751658</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-36.71140758787275,175.61349453316467</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-36.71188307397702,175.61422077352103</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-36.712347263346665,175.6149343832023</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-36.71278911234124,175.6156487817291</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-36.71322805734038,175.61638076812935</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-36.71366484542665,175.6171109389656</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-36.714083220879154,175.61784198045706</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-36.71451601133225,175.61858143058097</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-36.71491459889595,175.61935270930897</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-36.71529638911628,175.6201167055426</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-36.715671886563676,175.620899819021</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>-36.71603493198089,175.62169518525064</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>-36.71630875294311,175.62252851505485</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W355"/>
+  <dimension ref="A1:W357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27039,6 +27039,156 @@
         <v>322.15</v>
       </c>
       <c r="W355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>283.19</v>
+      </c>
+      <c r="C356" t="n">
+        <v>276.59</v>
+      </c>
+      <c r="D356" t="n">
+        <v>284.55</v>
+      </c>
+      <c r="E356" t="n">
+        <v>296.14</v>
+      </c>
+      <c r="F356" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="G356" t="n">
+        <v>295.84</v>
+      </c>
+      <c r="H356" t="n">
+        <v>294.97</v>
+      </c>
+      <c r="I356" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="J356" t="n">
+        <v>308.69</v>
+      </c>
+      <c r="K356" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="L356" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="M356" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="N356" t="n">
+        <v>329.29</v>
+      </c>
+      <c r="O356" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="P356" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>327.68</v>
+      </c>
+      <c r="R356" t="n">
+        <v>324.46</v>
+      </c>
+      <c r="S356" t="n">
+        <v>322.37</v>
+      </c>
+      <c r="T356" t="n">
+        <v>321.32</v>
+      </c>
+      <c r="U356" t="n">
+        <v>316.87</v>
+      </c>
+      <c r="V356" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:51+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>279.05</v>
+      </c>
+      <c r="C357" t="n">
+        <v>275.2</v>
+      </c>
+      <c r="D357" t="n">
+        <v>283.77</v>
+      </c>
+      <c r="E357" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="F357" t="n">
+        <v>299.84</v>
+      </c>
+      <c r="G357" t="n">
+        <v>295.46</v>
+      </c>
+      <c r="H357" t="n">
+        <v>294.61</v>
+      </c>
+      <c r="I357" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="J357" t="n">
+        <v>308.38</v>
+      </c>
+      <c r="K357" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="L357" t="n">
+        <v>320.12</v>
+      </c>
+      <c r="M357" t="n">
+        <v>324.22</v>
+      </c>
+      <c r="N357" t="n">
+        <v>328.56</v>
+      </c>
+      <c r="O357" t="n">
+        <v>326.93</v>
+      </c>
+      <c r="P357" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="R357" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="S357" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="T357" t="n">
+        <v>319.42</v>
+      </c>
+      <c r="U357" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="V357" t="n">
+        <v>314.96</v>
+      </c>
+      <c r="W357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27055,7 +27205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30638,6 +30788,26 @@
       </c>
       <c r="B358" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -30806,28 +30976,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.360785271818921</v>
+        <v>0.3488212812296283</v>
       </c>
       <c r="J2" t="n">
+        <v>356</v>
+      </c>
+      <c r="K2" t="n">
         <v>354</v>
       </c>
-      <c r="K2" t="n">
-        <v>352</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02388446653043341</v>
+        <v>0.02257031110447683</v>
       </c>
       <c r="M2" t="n">
-        <v>14.6359873477412</v>
+        <v>14.62225638441106</v>
       </c>
       <c r="N2" t="n">
-        <v>304.0043809182779</v>
+        <v>303.0005023586131</v>
       </c>
       <c r="O2" t="n">
-        <v>17.4357214051578</v>
+        <v>17.40690961539736</v>
       </c>
       <c r="P2" t="n">
-        <v>282.5002562464606</v>
+        <v>282.6303387599633</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30884,28 +31054,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2658593374681786</v>
+        <v>0.2495737774140244</v>
       </c>
       <c r="J3" t="n">
+        <v>356</v>
+      </c>
+      <c r="K3" t="n">
         <v>354</v>
       </c>
-      <c r="K3" t="n">
-        <v>352</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0277298111146268</v>
+        <v>0.0245865212975257</v>
       </c>
       <c r="M3" t="n">
-        <v>9.365904888234185</v>
+        <v>9.403241758791202</v>
       </c>
       <c r="N3" t="n">
-        <v>140.4249760746235</v>
+        <v>140.8966894844518</v>
       </c>
       <c r="O3" t="n">
-        <v>11.85010447526196</v>
+        <v>11.86999113245043</v>
       </c>
       <c r="P3" t="n">
-        <v>283.7832117158325</v>
+        <v>283.9612253733292</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30962,28 +31132,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2649323615520233</v>
+        <v>0.256569094981671</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0579879079080402</v>
+        <v>0.0549274503203766</v>
       </c>
       <c r="M4" t="n">
-        <v>6.692804661206342</v>
+        <v>6.695989130154998</v>
       </c>
       <c r="N4" t="n">
-        <v>65.02556677133872</v>
+        <v>64.9958794744142</v>
       </c>
       <c r="O4" t="n">
-        <v>8.063843176261473</v>
+        <v>8.062002200099812</v>
       </c>
       <c r="P4" t="n">
-        <v>284.7752253176993</v>
+        <v>284.8661928837746</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31040,28 +31210,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2240323337586957</v>
+        <v>0.2165110274416392</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05681567210128435</v>
+        <v>0.05357521205888727</v>
       </c>
       <c r="M5" t="n">
-        <v>5.745305072173358</v>
+        <v>5.752151225232057</v>
       </c>
       <c r="N5" t="n">
-        <v>47.51655222836266</v>
+        <v>47.52079315846031</v>
       </c>
       <c r="O5" t="n">
-        <v>6.893225096307436</v>
+        <v>6.893532705257901</v>
       </c>
       <c r="P5" t="n">
-        <v>296.8371095559792</v>
+        <v>296.9189185076867</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31118,28 +31288,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1498769031512799</v>
+        <v>0.1394067137164915</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03497975741214165</v>
+        <v>0.03031838472914106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.885518669388741</v>
+        <v>4.917411128640063</v>
       </c>
       <c r="N6" t="n">
-        <v>35.34143173818772</v>
+        <v>35.66908035415992</v>
       </c>
       <c r="O6" t="n">
-        <v>5.944865998337366</v>
+        <v>5.972359697318969</v>
       </c>
       <c r="P6" t="n">
-        <v>305.8184301816314</v>
+        <v>305.9323136479492</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31196,28 +31366,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1035666529261845</v>
+        <v>0.09683564712075467</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01793999657019851</v>
+        <v>0.01580127465986758</v>
       </c>
       <c r="M7" t="n">
-        <v>4.683601386858141</v>
+        <v>4.694068910774796</v>
       </c>
       <c r="N7" t="n">
-        <v>33.8171085000653</v>
+        <v>33.84796798375908</v>
       </c>
       <c r="O7" t="n">
-        <v>5.815247931091615</v>
+        <v>5.817900650901413</v>
       </c>
       <c r="P7" t="n">
-        <v>299.1698783189907</v>
+        <v>299.2425842857905</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31274,28 +31444,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1075314194379489</v>
+        <v>0.1024058275913455</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02364086382961861</v>
+        <v>0.02164062189159677</v>
       </c>
       <c r="M8" t="n">
-        <v>4.191129208880726</v>
+        <v>4.19469497686652</v>
       </c>
       <c r="N8" t="n">
-        <v>27.2340416908786</v>
+        <v>27.2069243942622</v>
       </c>
       <c r="O8" t="n">
-        <v>5.218624501808748</v>
+        <v>5.216025727914137</v>
       </c>
       <c r="P8" t="n">
-        <v>296.6561319125174</v>
+        <v>296.7118828379021</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31352,28 +31522,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1491550853452113</v>
+        <v>0.1477118868697987</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03661819200371319</v>
+        <v>0.03634171659984387</v>
       </c>
       <c r="M9" t="n">
-        <v>4.748831194135039</v>
+        <v>4.729680515767174</v>
       </c>
       <c r="N9" t="n">
-        <v>33.37895692912486</v>
+        <v>33.2009067094114</v>
       </c>
       <c r="O9" t="n">
-        <v>5.777452460135424</v>
+        <v>5.762022796675782</v>
       </c>
       <c r="P9" t="n">
-        <v>300.107570653991</v>
+        <v>300.1232680268823</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31430,28 +31600,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08085645300390649</v>
+        <v>0.07499630928690881</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01271177854146122</v>
+        <v>0.01102243585470764</v>
       </c>
       <c r="M10" t="n">
-        <v>4.413277067202875</v>
+        <v>4.41528536553089</v>
       </c>
       <c r="N10" t="n">
-        <v>28.95756881524193</v>
+        <v>28.95943425043744</v>
       </c>
       <c r="O10" t="n">
-        <v>5.381223728413634</v>
+        <v>5.381397053780499</v>
       </c>
       <c r="P10" t="n">
-        <v>311.8081319897843</v>
+        <v>311.8718723153851</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31508,28 +31678,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04806982065593815</v>
+        <v>0.04409067280081188</v>
       </c>
       <c r="J11" t="n">
+        <v>356</v>
+      </c>
+      <c r="K11" t="n">
         <v>354</v>
       </c>
-      <c r="K11" t="n">
-        <v>352</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.005212295861693916</v>
+        <v>0.004427745216463941</v>
       </c>
       <c r="M11" t="n">
-        <v>4.127628163643214</v>
+        <v>4.127127932977198</v>
       </c>
       <c r="N11" t="n">
-        <v>24.90445226817645</v>
+        <v>24.83912814962129</v>
       </c>
       <c r="O11" t="n">
-        <v>4.990436079960994</v>
+        <v>4.983886851607016</v>
       </c>
       <c r="P11" t="n">
-        <v>320.0562659540278</v>
+        <v>320.099844849626</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31586,28 +31756,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.130291502965083</v>
+        <v>0.1257404190439859</v>
       </c>
       <c r="J12" t="n">
+        <v>356</v>
+      </c>
+      <c r="K12" t="n">
         <v>354</v>
       </c>
-      <c r="K12" t="n">
-        <v>352</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0479531337107425</v>
+        <v>0.0450987912431835</v>
       </c>
       <c r="M12" t="n">
-        <v>3.487513134194399</v>
+        <v>3.493069410123906</v>
       </c>
       <c r="N12" t="n">
-        <v>19.03286485611118</v>
+        <v>19.02374787942453</v>
       </c>
       <c r="O12" t="n">
-        <v>4.362667172282476</v>
+        <v>4.361622161469804</v>
       </c>
       <c r="P12" t="n">
-        <v>321.0532504023805</v>
+        <v>321.1030926989321</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31664,28 +31834,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07280834420758309</v>
+        <v>0.07015994036736434</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01208991092325939</v>
+        <v>0.0113523620126077</v>
       </c>
       <c r="M13" t="n">
-        <v>3.717878151663915</v>
+        <v>3.710814062629028</v>
       </c>
       <c r="N13" t="n">
-        <v>24.94810422184958</v>
+        <v>24.84306243945305</v>
       </c>
       <c r="O13" t="n">
-        <v>4.994807726214251</v>
+        <v>4.9842815369372</v>
       </c>
       <c r="P13" t="n">
-        <v>325.1509248286324</v>
+        <v>325.1795338673634</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31742,28 +31912,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1058986128925638</v>
+        <v>0.1031089789879012</v>
       </c>
       <c r="J14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02239080933444615</v>
+        <v>0.02146992319305896</v>
       </c>
       <c r="M14" t="n">
-        <v>4.238895596760202</v>
+        <v>4.230116407390935</v>
       </c>
       <c r="N14" t="n">
-        <v>28.20050906261795</v>
+        <v>28.08070894373113</v>
       </c>
       <c r="O14" t="n">
-        <v>5.310415149742809</v>
+        <v>5.299123412766599</v>
       </c>
       <c r="P14" t="n">
-        <v>328.6806738625826</v>
+        <v>328.7108081047413</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31820,28 +31990,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09955581288233654</v>
+        <v>0.0958634180381963</v>
       </c>
       <c r="J15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01665683245661587</v>
+        <v>0.0156130583514611</v>
       </c>
       <c r="M15" t="n">
-        <v>4.798041193256213</v>
+        <v>4.789079607379604</v>
       </c>
       <c r="N15" t="n">
-        <v>33.69976354644027</v>
+        <v>33.57802034364578</v>
       </c>
       <c r="O15" t="n">
-        <v>5.805149743670723</v>
+        <v>5.794654462834326</v>
       </c>
       <c r="P15" t="n">
-        <v>328.1673153073896</v>
+        <v>328.2072012704009</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31898,28 +32068,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05050403075400599</v>
+        <v>0.04736130585266435</v>
       </c>
       <c r="J16" t="n">
+        <v>356</v>
+      </c>
+      <c r="K16" t="n">
         <v>354</v>
       </c>
-      <c r="K16" t="n">
-        <v>352</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.004550690819305592</v>
+        <v>0.004045771763619643</v>
       </c>
       <c r="M16" t="n">
-        <v>4.610732681778701</v>
+        <v>4.601947973281058</v>
       </c>
       <c r="N16" t="n">
-        <v>31.50826887175585</v>
+        <v>31.37892571318902</v>
       </c>
       <c r="O16" t="n">
-        <v>5.613222681468806</v>
+        <v>5.601689540950036</v>
       </c>
       <c r="P16" t="n">
-        <v>329.1508574790944</v>
+        <v>329.1852780964896</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31976,28 +32146,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08151023523899074</v>
+        <v>0.07509324490601892</v>
       </c>
       <c r="J17" t="n">
+        <v>356</v>
+      </c>
+      <c r="K17" t="n">
         <v>354</v>
       </c>
-      <c r="K17" t="n">
-        <v>352</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.007859834374325247</v>
+        <v>0.006730784930475076</v>
       </c>
       <c r="M17" t="n">
-        <v>5.70213569447555</v>
+        <v>5.699626797434633</v>
       </c>
       <c r="N17" t="n">
-        <v>47.3603138816183</v>
+        <v>47.2885217445795</v>
       </c>
       <c r="O17" t="n">
-        <v>6.881883018594424</v>
+        <v>6.876665016167321</v>
       </c>
       <c r="P17" t="n">
-        <v>330.9986460724975</v>
+        <v>331.0689234644183</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32054,28 +32224,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08781326524929094</v>
+        <v>0.08066507565365016</v>
       </c>
       <c r="J18" t="n">
+        <v>356</v>
+      </c>
+      <c r="K18" t="n">
         <v>354</v>
       </c>
-      <c r="K18" t="n">
-        <v>352</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01033984003955513</v>
+        <v>0.008791834297211198</v>
       </c>
       <c r="M18" t="n">
-        <v>5.31222141456718</v>
+        <v>5.315380613022209</v>
       </c>
       <c r="N18" t="n">
-        <v>41.6795634490805</v>
+        <v>41.6878215977037</v>
       </c>
       <c r="O18" t="n">
-        <v>6.455971146859356</v>
+        <v>6.456610689650081</v>
       </c>
       <c r="P18" t="n">
-        <v>328.1044367956002</v>
+        <v>328.1827229050707</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32132,28 +32302,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1326809917920969</v>
+        <v>0.1239378710854993</v>
       </c>
       <c r="J19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K19" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L19" t="n">
-        <v>0.016399700906082</v>
+        <v>0.01442035190720137</v>
       </c>
       <c r="M19" t="n">
-        <v>6.460558469507879</v>
+        <v>6.47089766790503</v>
       </c>
       <c r="N19" t="n">
-        <v>60.21368838815928</v>
+        <v>60.2456040196593</v>
       </c>
       <c r="O19" t="n">
-        <v>7.75974795906151</v>
+        <v>7.761804172978039</v>
       </c>
       <c r="P19" t="n">
-        <v>326.057182746849</v>
+        <v>326.1522845610744</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32210,28 +32380,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06895157043350846</v>
+        <v>0.05865697315945658</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K20" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004693521684171365</v>
+        <v>0.003411010863017538</v>
       </c>
       <c r="M20" t="n">
-        <v>6.45438940883668</v>
+        <v>6.468205556753728</v>
       </c>
       <c r="N20" t="n">
-        <v>57.49650072478298</v>
+        <v>57.68643630080111</v>
       </c>
       <c r="O20" t="n">
-        <v>7.582644705166066</v>
+        <v>7.59515874098765</v>
       </c>
       <c r="P20" t="n">
-        <v>328.0917606417262</v>
+        <v>328.203738022452</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32288,28 +32458,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1453150013985004</v>
+        <v>0.1316973795007614</v>
       </c>
       <c r="J21" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K21" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01405957377975697</v>
+        <v>0.01159112027176934</v>
       </c>
       <c r="M21" t="n">
-        <v>7.650692864384577</v>
+        <v>7.672646895536426</v>
       </c>
       <c r="N21" t="n">
-        <v>84.44899930263101</v>
+        <v>84.8724862110565</v>
       </c>
       <c r="O21" t="n">
-        <v>9.189613664492704</v>
+        <v>9.21262645563449</v>
       </c>
       <c r="P21" t="n">
-        <v>324.3511879931287</v>
+        <v>324.4993109415018</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32366,28 +32536,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1095552097710625</v>
+        <v>0.09563527663618622</v>
       </c>
       <c r="J22" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K22" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01048071338664502</v>
+        <v>0.007976874168251324</v>
       </c>
       <c r="M22" t="n">
-        <v>6.586555588830413</v>
+        <v>6.615384018928451</v>
       </c>
       <c r="N22" t="n">
-        <v>64.9893923838372</v>
+        <v>65.63539037345819</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0615998650291</v>
+        <v>8.101567155400133</v>
       </c>
       <c r="P22" t="n">
-        <v>328.6438520360383</v>
+        <v>328.7951053853245</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32425,7 +32595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W355"/>
+  <dimension ref="A1:W357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73855,6 +74025,240 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-36.70694137012654,175.60882504995652</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-36.70756551805114,175.60928207065854</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-36.708112399127025,175.60987073939464</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-36.708640012501945,175.61049223052547</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-36.70922010612308,175.6110600011423</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-36.709830345951474,175.61160492829876</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-36.710386964768134,175.6121994908449</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-36.71088157983626,175.61285598385518</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-36.71139761349604,175.61350745741586</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-36.711871653798084,175.61423361507318</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-36.71233340741918,175.6149486882769</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-36.71277431928162,175.6156637857139</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-36.713211902751695,175.61639578893477</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-36.71365014260016,175.61712367991015</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-36.71406962626256,175.61785376100065</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-36.7145029183974,175.61859172371737</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-36.71490347513548,175.61936055610096</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-36.71528485475502,175.62012478713746</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-36.71566294713759,175.6209056306137</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>-36.71602924975828,175.62169858232434</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>-36.716307209004675,175.62252943292407</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:51+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-36.7069633388339,175.60878761726016</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-36.7075728940495,175.60926950260904</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-36.708116538200834,175.60986368679585</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-36.70864261270576,175.61048780003367</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-36.709223204380415,175.61105505612218</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-36.70983258858445,175.611601715842</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-36.71038914165529,175.61219650499</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-36.71088157983626,175.61285598385518</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-36.71139954603162,175.61350495334244</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-36.71187539373986,175.61422940965303</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-36.71233700996048,175.61494496895799</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-36.712780110904234,175.615657911513</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-36.71321716741694,175.61639089376226</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-36.713656939886924,175.6171177896248</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-36.71407827066562,175.61784627011198</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-36.71450900813464,175.6185869362125</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-36.71491256215111,175.61935414604568</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-36.71529842920734,175.62011527614465</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-36.71567811223527,175.620895771661</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>-36.71604986810854,175.6216862557975</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>-36.716367178819304,175.62249378092645</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
